--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-09-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E8886E-2871-42B3-8F2E-DF699318409E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A45271-FE08-4360-B9DC-8A3FF88CD843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30705" yWindow="2100" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -766,9 +766,6 @@
     <t>£39.88</t>
   </si>
   <si>
-    <t>£44.94</t>
-  </si>
-  <si>
     <t>£46.62</t>
   </si>
   <si>
@@ -799,9 +796,6 @@
     <t>£52.0</t>
   </si>
   <si>
-    <t>£54.68</t>
-  </si>
-  <si>
     <t>£56.65</t>
   </si>
   <si>
@@ -838,9 +832,6 @@
     <t>£55.9</t>
   </si>
   <si>
-    <t>£58.58</t>
-  </si>
-  <si>
     <t>£61.04</t>
   </si>
   <si>
@@ -877,9 +868,6 @@
     <t>£60.99</t>
   </si>
   <si>
-    <t>£70.33</t>
-  </si>
-  <si>
     <t>£69.38</t>
   </si>
   <si>
@@ -910,9 +898,6 @@
     <t>£69.21</t>
   </si>
   <si>
-    <t>£68.25</t>
-  </si>
-  <si>
     <t>£76.12</t>
   </si>
   <si>
@@ -946,9 +931,6 @@
     <t>£69.12</t>
   </si>
   <si>
-    <t>£66.11</t>
-  </si>
-  <si>
     <t>£74.93</t>
   </si>
   <si>
@@ -1003,9 +985,6 @@
     <t>£65.45</t>
   </si>
   <si>
-    <t>£63.73</t>
-  </si>
-  <si>
     <t>£72.21</t>
   </si>
   <si>
@@ -1184,6 +1163,27 @@
   </si>
   <si>
     <t>£1850.00</t>
+  </si>
+  <si>
+    <t>£41.49</t>
+  </si>
+  <si>
+    <t>£49.57</t>
+  </si>
+  <si>
+    <t>£53.22</t>
+  </si>
+  <si>
+    <t>£59.29</t>
+  </si>
+  <si>
+    <t>£68.51</t>
+  </si>
+  <si>
+    <t>£62.42</t>
+  </si>
+  <si>
+    <t>£62.06</t>
   </si>
 </sst>
 </file>
@@ -1746,7 +1746,7 @@
         <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="K4" t="s">
         <v>53</v>
@@ -1858,7 +1858,7 @@
         <v>79</v>
       </c>
       <c r="J6" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="K6" t="s">
         <v>80</v>
@@ -1914,7 +1914,7 @@
         <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="K7" t="s">
         <v>93</v>
@@ -2082,7 +2082,7 @@
         <v>132</v>
       </c>
       <c r="J10" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="K10" t="s">
         <v>133</v>
@@ -2138,7 +2138,7 @@
         <v>144</v>
       </c>
       <c r="J11" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="K11" t="s">
         <v>133</v>
@@ -2194,7 +2194,7 @@
         <v>156</v>
       </c>
       <c r="J12" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="K12" t="s">
         <v>157</v>
@@ -2250,7 +2250,7 @@
         <v>169</v>
       </c>
       <c r="J13" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="K13" t="s">
         <v>170</v>
@@ -2306,7 +2306,7 @@
         <v>182</v>
       </c>
       <c r="J14" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="K14" t="s">
         <v>183</v>
@@ -2362,7 +2362,7 @@
         <v>194</v>
       </c>
       <c r="J15" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="K15" t="s">
         <v>195</v>
@@ -2530,7 +2530,7 @@
         <v>229</v>
       </c>
       <c r="J18" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="K18" t="s">
         <v>230</v>
@@ -2574,7 +2574,7 @@
         <v>239</v>
       </c>
       <c r="F19" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="G19" t="s">
         <v>240</v>
@@ -2586,7 +2586,7 @@
         <v>242</v>
       </c>
       <c r="J19" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="K19" t="s">
         <v>243</v>
@@ -2607,307 +2607,307 @@
         <v>247</v>
       </c>
       <c r="Q19" t="s">
+        <v>381</v>
+      </c>
+      <c r="R19" t="s">
         <v>248</v>
-      </c>
-      <c r="R19" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>249</v>
+      </c>
+      <c r="B20" t="s">
         <v>250</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>251</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20" t="s">
+        <v>251</v>
+      </c>
+      <c r="F20" t="s">
+        <v>373</v>
+      </c>
+      <c r="G20" t="s">
         <v>252</v>
       </c>
-      <c r="D20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" t="s">
-        <v>252</v>
-      </c>
-      <c r="F20" t="s">
-        <v>380</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>253</v>
-      </c>
-      <c r="H20" t="s">
-        <v>254</v>
       </c>
       <c r="I20" t="s">
         <v>194</v>
       </c>
       <c r="J20" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="K20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
       </c>
       <c r="M20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N20" t="s">
         <v>245</v>
       </c>
       <c r="O20" t="s">
+        <v>256</v>
+      </c>
+      <c r="P20" t="s">
         <v>257</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
+        <v>382</v>
+      </c>
+      <c r="R20" t="s">
         <v>258</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>259</v>
-      </c>
-      <c r="R20" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C21" t="s">
         <v>261</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F21" t="s">
+        <v>374</v>
+      </c>
+      <c r="G21" t="s">
         <v>262</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" t="s">
         <v>263</v>
       </c>
-      <c r="D21" t="s">
-        <v>263</v>
-      </c>
-      <c r="E21" t="s">
-        <v>263</v>
-      </c>
-      <c r="F21" t="s">
-        <v>381</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>264</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>265</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>266</v>
-      </c>
-      <c r="J21" t="s">
-        <v>267</v>
-      </c>
-      <c r="K21" t="s">
-        <v>268</v>
       </c>
       <c r="L21" t="s">
         <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N21" t="s">
         <v>245</v>
       </c>
       <c r="O21" t="s">
+        <v>268</v>
+      </c>
+      <c r="P21" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>383</v>
+      </c>
+      <c r="R21" t="s">
         <v>270</v>
-      </c>
-      <c r="P21" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>272</v>
-      </c>
-      <c r="R21" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>271</v>
+      </c>
+      <c r="B22" t="s">
+        <v>272</v>
+      </c>
+      <c r="C22" t="s">
+        <v>273</v>
+      </c>
+      <c r="D22" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" t="s">
+        <v>273</v>
+      </c>
+      <c r="F22" t="s">
+        <v>375</v>
+      </c>
+      <c r="G22" t="s">
         <v>274</v>
       </c>
-      <c r="B22" t="s">
+      <c r="H22" t="s">
         <v>275</v>
       </c>
-      <c r="C22" t="s">
+      <c r="I22" t="s">
         <v>276</v>
       </c>
-      <c r="D22" t="s">
-        <v>276</v>
-      </c>
-      <c r="E22" t="s">
-        <v>276</v>
-      </c>
-      <c r="F22" t="s">
-        <v>382</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="J22" t="s">
         <v>277</v>
       </c>
-      <c r="H22" t="s">
+      <c r="K22" t="s">
         <v>278</v>
-      </c>
-      <c r="I22" t="s">
-        <v>279</v>
-      </c>
-      <c r="J22" t="s">
-        <v>280</v>
-      </c>
-      <c r="K22" t="s">
-        <v>281</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
       </c>
       <c r="M22" t="s">
+        <v>279</v>
+      </c>
+      <c r="N22" t="s">
+        <v>354</v>
+      </c>
+      <c r="O22" t="s">
+        <v>280</v>
+      </c>
+      <c r="P22" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>384</v>
+      </c>
+      <c r="R22" t="s">
         <v>282</v>
-      </c>
-      <c r="N22" t="s">
-        <v>361</v>
-      </c>
-      <c r="O22" t="s">
-        <v>283</v>
-      </c>
-      <c r="P22" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>285</v>
-      </c>
-      <c r="R22" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B23" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C23" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D23" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E23" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F23" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G23" t="s">
         <v>155</v>
       </c>
       <c r="H23" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I23" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J23" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="K23" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="N23" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="O23" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="P23" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="Q23" t="s">
-        <v>296</v>
+        <v>385</v>
       </c>
       <c r="R23" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B24" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C24" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E24" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F24" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="G24" t="s">
         <v>155</v>
       </c>
       <c r="H24" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="I24" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="J24" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K24" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="N24" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="O24" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="P24" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="Q24" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="R24" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B25" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E25" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F25" t="s">
         <v>155</v>
@@ -2922,7 +2922,7 @@
         <v>155</v>
       </c>
       <c r="J25" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="K25" t="s">
         <v>155</v>
@@ -2931,13 +2931,13 @@
         <v>155</v>
       </c>
       <c r="M25" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N25" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="O25" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="P25" t="s">
         <v>155</v>
@@ -2951,226 +2951,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B26" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C26" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="D26" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E26" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F26" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="G26" t="s">
         <v>155</v>
       </c>
       <c r="H26" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="I26" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="J26" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="K26" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L26" t="s">
         <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="N26" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="O26" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="P26" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="Q26" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="R26" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B27" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C27" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="D27" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E27" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="F27" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="G27" t="s">
         <v>155</v>
       </c>
       <c r="H27" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="I27" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="J27" t="s">
         <v>155</v>
       </c>
       <c r="K27" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N27" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="O27" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="P27" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Q27" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="R27" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B28" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C28" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D28" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E28" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F28" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="G28" t="s">
         <v>155</v>
       </c>
       <c r="H28" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="I28" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="J28" t="s">
         <v>155</v>
       </c>
       <c r="K28" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="N28" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="O28" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="P28" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="Q28" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="R28" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C29" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D29" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E29" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="F29" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="G29" t="s">
         <v>155</v>
       </c>
       <c r="H29" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I29" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="J29" t="s">
         <v>155</v>
       </c>
       <c r="K29" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="L29" t="s">
         <v>155</v>
       </c>
       <c r="M29" t="s">
+        <v>350</v>
+      </c>
+      <c r="N29" t="s">
         <v>357</v>
       </c>
-      <c r="N29" t="s">
-        <v>364</v>
-      </c>
       <c r="O29" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="P29" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="Q29" t="s">
         <v>155</v>
       </c>
       <c r="R29" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
